--- a/produtos_afiliados-1.xlsx
+++ b/produtos_afiliados-1.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="50">
   <si>
     <t>loja</t>
   </si>
@@ -133,12 +133,60 @@
   <si>
     <t>Dica: use a aba Lojas para controlar quais programas de afiliados já estão ativos (lista da loja vem dali).</t>
   </si>
+  <si>
+    <t>Bicicleta Aro 29 Mtb Cripto 24v Freios a Disco</t>
+  </si>
+  <si>
+    <t>https://meli.la/2yK4C1b</t>
+  </si>
+  <si>
+    <t>Kit Gamer: Teclado Semi MecÃ¢nico RGB + Mouse RGB Ãptico + Mouse Pad Profissional, PC, Notebook, Xbox, PS5</t>
+  </si>
+  <si>
+    <t>https://s.shopee.com.br/6fi8Ux6Jal</t>
+  </si>
+  <si>
+    <t>Piscina Estrutural 6473 Litros + Bomba Filtrante + Capa + Forro Bestway</t>
+  </si>
+  <si>
+    <t>https://s.shopee.com.br/3qNx2tBAPe</t>
+  </si>
+  <si>
+    <t>Varal Luz 20m Externo com LÃ¢mpada LED Quente Gambiarra Preto</t>
+  </si>
+  <si>
+    <t>https://meli.la/2ao7fiP</t>
+  </si>
+  <si>
+    <t>https://meli.la/1ESVqWQ</t>
+  </si>
+  <si>
+    <t>Trenzinho Natalino para Ãrvore de Natal com Luz, Movimento e Som</t>
+  </si>
+  <si>
+    <t>https://meli.la/1G86cvo</t>
+  </si>
+  <si>
+    <t>https://meli.la/2rinBuV</t>
+  </si>
+  <si>
+    <t>Projetor de Natal LED Desenhos Natalinos Luz Decorativa 127/220v</t>
+  </si>
+  <si>
+    <t>https://meli.la/29A8Lf4</t>
+  </si>
+  <si>
+    <t>Vila Natalina com Luz LED, Casinhas e Igreja, Decoração de Natal</t>
+  </si>
+  <si>
+    <t>Pisca-pisca Solar LED para Exterior, Decoraçãoo de Natal Multicolor com 8 Modos de Luz</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,6 +230,28 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="18"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="18"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -197,7 +267,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -214,11 +284,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -239,8 +325,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -572,39 +665,67 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="3"/>
+      <c r="A3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="12">
+        <v>1499</v>
+      </c>
+      <c r="D3" s="12">
+        <v>761.76</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="F3" s="3"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="5" t="str">
+      <c r="I3" s="5">
         <f>IF(AND(ISNUMBER(C3),ISNUMBER(D3),C3&gt;0),1-D3/C3,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="3"/>
+        <v>0.49182121414276181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="12">
+        <v>125.89</v>
+      </c>
+      <c r="D4" s="12">
+        <v>54.99</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>35</v>
+      </c>
       <c r="F4" s="3"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="5" t="str">
+      <c r="I4" s="5">
         <f>IF(AND(ISNUMBER(C4),ISNUMBER(D4),C4&gt;0),1-D4/C4,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="3"/>
+        <v>0.56319008658352532</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="24.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12">
+        <v>1212.33</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>37</v>
+      </c>
       <c r="F5" s="3"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -613,74 +734,124 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="3"/>
+    <row r="6" spans="1:9" ht="24.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="12">
+        <v>159</v>
+      </c>
+      <c r="D6" s="12">
+        <v>118</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>39</v>
+      </c>
       <c r="F6" s="3"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="5" t="str">
+      <c r="I6" s="5">
         <f>IF(AND(ISNUMBER(C6),ISNUMBER(D6),C6&gt;0),1-D6/C6,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="3"/>
+        <v>0.25786163522012584</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="24.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="12">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="D7" s="12">
+        <v>54.27</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>40</v>
+      </c>
       <c r="F7" s="3"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="5" t="str">
+      <c r="I7" s="5">
         <f>IF(AND(ISNUMBER(C7),ISNUMBER(D7),C7&gt;0),1-D7/C7,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="3"/>
+        <v>0.31216730038022811</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="24.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="12">
+        <v>599.9</v>
+      </c>
+      <c r="D8" s="12">
+        <v>273.89999999999998</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>42</v>
+      </c>
       <c r="F8" s="3"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="5" t="str">
+      <c r="I8" s="5">
         <f>IF(AND(ISNUMBER(C8),ISNUMBER(D8),C8&gt;0),1-D8/C8,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="3"/>
+        <v>0.54342390398399743</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="24.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="12">
+        <v>82</v>
+      </c>
+      <c r="D9" s="12">
+        <v>53.29</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="F9" s="3"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="5" t="str">
+      <c r="I9" s="5">
         <f>IF(AND(ISNUMBER(C9),ISNUMBER(D9),C9&gt;0),1-D9/C9,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="3"/>
+        <v>0.35012195121951217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="24.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="12">
+        <v>59</v>
+      </c>
+      <c r="D10" s="12">
+        <v>46.35</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="F10" s="3"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="5" t="str">
+      <c r="I10" s="5">
         <f>IF(AND(ISNUMBER(C10),ISNUMBER(D10),C10&gt;0),1-D10/C10,"")</f>
-        <v/>
+        <v>0.21440677966101696</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -7551,6 +7722,16 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{2C2212FD-AEBB-2E46-83B0-2D6F8C98F1BE}"/>
+    <hyperlink ref="E4" r:id="rId2" xr:uid="{4764F83C-C63E-284C-B600-6C323259D61C}"/>
+    <hyperlink ref="E5" r:id="rId3" xr:uid="{1F4CBB06-C81D-FF43-98A3-F5D104B4CE37}"/>
+    <hyperlink ref="E6" r:id="rId4" xr:uid="{78EE1DC1-AB52-B84A-98DB-0F7D1BA8F5A0}"/>
+    <hyperlink ref="E7" r:id="rId5" xr:uid="{D8712E49-46B4-A849-A111-1EAD7049BE5E}"/>
+    <hyperlink ref="E8" r:id="rId6" xr:uid="{0DD9901A-FE61-7841-B514-5CC51D17BFCB}"/>
+    <hyperlink ref="E9" r:id="rId7" xr:uid="{834F7830-9B31-DE4C-9C2E-A2DD57FB1EF7}"/>
+    <hyperlink ref="E10" r:id="rId8" xr:uid="{BEA1357F-1C5A-0F4E-80BB-065400E403EB}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <extLst>
@@ -7563,7 +7744,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>A2:A500</xm:sqref>
+          <xm:sqref>A2 A11:A500</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
